--- a/backend/data/financials_by_company/0VG.F.xlsx
+++ b/backend/data/financials_by_company/0VG.F.xlsx
@@ -642,49 +642,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>56692.913386</v>
+        <v>-7030000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007874000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>-26800000</v>
+        <v>244300000</v>
       </c>
       <c r="E2" t="n">
-        <v>7200000</v>
+        <v>-37000000</v>
       </c>
       <c r="F2" t="n">
-        <v>7200000</v>
+        <v>-37000000</v>
       </c>
       <c r="G2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="H2" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="I2" t="n">
-        <v>10500000</v>
+        <v>27300000</v>
       </c>
       <c r="J2" t="n">
-        <v>-19600000</v>
+        <v>207300000</v>
       </c>
       <c r="K2" t="n">
-        <v>-19900000</v>
+        <v>206500000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-1600000</v>
       </c>
       <c r="M2" t="n">
-        <v>-19743307.086614</v>
+        <v>199570000</v>
       </c>
       <c r="N2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="O2" t="n">
-        <v>29900000</v>
+        <v>-116900000</v>
       </c>
       <c r="P2" t="n">
         <v>475300000</v>
@@ -693,79 +693,85 @@
         <v>475300000</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.027</v>
+        <v>0.357</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.027</v>
+        <v>0.357</v>
       </c>
       <c r="T2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="U2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="X2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-12600000</v>
+        <v>169600000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-100000</v>
+        <v>-1700000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-12700000</v>
+        <v>167900000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7200000</v>
+        <v>-37000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-7200000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>37000000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>-1600000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1600000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-19900000</v>
+        <v>206500000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19400000</v>
+        <v>-144200000</v>
       </c>
       <c r="AI2" t="n">
-        <v>16200000</v>
+        <v>1200000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="AK2" t="n">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>8600000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="n">
-        <v>3200000</v>
+        <v>8600000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-500000</v>
+        <v>62300000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10500000</v>
+        <v>27300000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10000000</v>
+        <v>89600000</v>
       </c>
       <c r="AR2" t="n">
-        <v>10000000</v>
+        <v>89600000</v>
       </c>
     </row>
     <row r="3">
@@ -900,49 +906,49 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>-7030000</v>
+        <v>56692.913386</v>
       </c>
       <c r="C4" t="n">
-        <v>0.19</v>
+        <v>0.007874000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>244300000</v>
+        <v>-26800000</v>
       </c>
       <c r="E4" t="n">
-        <v>-37000000</v>
+        <v>7200000</v>
       </c>
       <c r="F4" t="n">
-        <v>-37000000</v>
+        <v>7200000</v>
       </c>
       <c r="G4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="H4" t="n">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="I4" t="n">
-        <v>27300000</v>
+        <v>10500000</v>
       </c>
       <c r="J4" t="n">
-        <v>207300000</v>
+        <v>-19600000</v>
       </c>
       <c r="K4" t="n">
-        <v>206500000</v>
+        <v>-19900000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1600000</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>199570000</v>
+        <v>-19743307.086614</v>
       </c>
       <c r="N4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="O4" t="n">
-        <v>-116900000</v>
+        <v>29900000</v>
       </c>
       <c r="P4" t="n">
         <v>475300000</v>
@@ -951,85 +957,79 @@
         <v>475300000</v>
       </c>
       <c r="R4" t="n">
-        <v>0.357</v>
+        <v>-0.027</v>
       </c>
       <c r="S4" t="n">
-        <v>0.357</v>
+        <v>-0.027</v>
       </c>
       <c r="T4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="U4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="X4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="Y4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1700000</v>
+        <v>-100000</v>
       </c>
       <c r="AA4" t="n">
-        <v>167900000</v>
+        <v>-12700000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-37000000</v>
+        <v>7200000</v>
       </c>
       <c r="AC4" t="n">
-        <v>37000000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+        <v>-7200000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-1600000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1600000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>206500000</v>
+        <v>-19900000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-144200000</v>
+        <v>19400000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1200000</v>
+        <v>16200000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="AK4" t="n">
-        <v>800000</v>
+        <v>400000</v>
       </c>
       <c r="AL4" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
+        <v>3200000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>8600000</v>
+        <v>3200000</v>
       </c>
       <c r="AO4" t="n">
-        <v>62300000</v>
+        <v>-500000</v>
       </c>
       <c r="AP4" t="n">
-        <v>27300000</v>
+        <v>10500000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>89600000</v>
+        <v>10000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>89600000</v>
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>
@@ -1305,11 +1305,9 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44651</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>475333760</v>
       </c>
@@ -1317,122 +1315,146 @@
         <v>475333760</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>50600000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>47898000</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>97598000</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>168500000</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>47898000</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>47898000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>97598000</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>47898000</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>47898000</v>
       </c>
       <c r="O2" t="n">
         <v>10000</v>
       </c>
       <c r="P2" t="n">
-        <v>86100000</v>
+        <v>133900000</v>
       </c>
       <c r="Q2" t="n">
         <v>207900000</v>
       </c>
       <c r="R2" t="n">
-        <v>1200000</v>
+        <v>1188000</v>
       </c>
       <c r="S2" t="n">
-        <v>1200000</v>
+        <v>1188000</v>
       </c>
       <c r="T2" t="n">
-        <v>178200000</v>
+        <v>237102000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>147302000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>50300000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>600000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>49700000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>97000000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>178200000</v>
+        <v>89800000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>300000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
       <c r="AF2" t="n">
-        <v>175100000</v>
+        <v>82800000</v>
       </c>
       <c r="AG2" t="n">
-        <v>2400000</v>
+        <v>2700000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2000000</v>
+        <v>1900000</v>
       </c>
       <c r="AI2" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="AK2" t="n">
-        <v>178200000</v>
+        <v>285000000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>26700000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1900000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>178200000</v>
+        <v>258300000</v>
       </c>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
       <c r="AT2" t="n">
-        <v>2700000</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>84500000</v>
+        <v>7600000</v>
       </c>
       <c r="AV2" t="n">
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="AW2" t="n">
-        <v>100000</v>
+        <v>700000</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>114800000</v>
       </c>
       <c r="AY2" t="n">
-        <v>90400000</v>
+        <v>133600000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>90400000</v>
+        <v>133600000</v>
       </c>
     </row>
     <row r="3">
@@ -1581,9 +1603,11 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>475333760</v>
       </c>
@@ -1591,146 +1615,122 @@
         <v>475333760</v>
       </c>
       <c r="E4" t="n">
-        <v>50600000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>47898000</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>97598000</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>168500000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>47898000</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>47898000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>97598000</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>47898000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>47898000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>10000</v>
       </c>
       <c r="P4" t="n">
-        <v>133900000</v>
+        <v>86100000</v>
       </c>
       <c r="Q4" t="n">
         <v>207900000</v>
       </c>
       <c r="R4" t="n">
-        <v>1188000</v>
+        <v>1200000</v>
       </c>
       <c r="S4" t="n">
-        <v>1188000</v>
+        <v>1200000</v>
       </c>
       <c r="T4" t="n">
-        <v>237102000</v>
+        <v>178200000</v>
       </c>
       <c r="U4" t="n">
-        <v>147302000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>50300000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>49700000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>97000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>89800000</v>
+        <v>178200000</v>
       </c>
       <c r="AB4" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>82800000</v>
+        <v>175100000</v>
       </c>
       <c r="AG4" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>178200000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>178200000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
         <v>2700000</v>
       </c>
-      <c r="AH4" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>26700000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-600000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>258300000</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
       <c r="AU4" t="n">
-        <v>7600000</v>
+        <v>84500000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="AW4" t="n">
-        <v>700000</v>
+        <v>100000</v>
       </c>
       <c r="AX4" t="n">
-        <v>114800000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>133600000</v>
+        <v>90400000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>133600000</v>
+        <v>90400000</v>
       </c>
     </row>
   </sheetData>
@@ -1901,79 +1901,93 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45382</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>205500000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-248500000</v>
+      </c>
       <c r="D2" t="n">
-        <v>174900000</v>
+        <v>141200000</v>
       </c>
       <c r="E2" t="n">
+        <v>184200000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-43000000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-248800000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-248500000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-248500000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-248500000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-248500000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>205500000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-18500000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-6200000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-6300000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-80400000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-156600000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1700000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
         <v>169600000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>800000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-1800000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-2800000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-8200000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13900000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-12600000</v>
       </c>
     </row>
     <row r="3">
@@ -2063,93 +2077,79 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45382</v>
       </c>
       <c r="B4" t="n">
-        <v>205500000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-248500000</v>
-      </c>
+        <v>5400000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>141200000</v>
+        <v>174900000</v>
       </c>
       <c r="E4" t="n">
-        <v>184200000</v>
+        <v>169600000</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-43000000</v>
+        <v>5300000</v>
       </c>
       <c r="H4" t="n">
-        <v>-248800000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-248500000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-248500000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-248500000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-248500000</v>
-      </c>
-      <c r="M4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1800000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-2800000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-8200000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="AB4" t="n">
         <v>300000</v>
       </c>
-      <c r="N4" t="n">
+      <c r="AC4" t="n">
         <v>300000</v>
       </c>
-      <c r="O4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>205500000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>200000</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>-18500000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-6200000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-6300000</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="AD4" t="n">
         <v>100000</v>
       </c>
-      <c r="X4" t="n">
-        <v>-80400000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-156600000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1700000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>169600000</v>
+        <v>-12600000</v>
       </c>
     </row>
   </sheetData>
@@ -2163,7 +2163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB2"/>
+  <dimension ref="A1:EI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,415 +2414,450 @@
       </c>
       <c r="AX1" t="inlineStr">
         <is>
+          <t>priceToSalesTrailing12Months</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>enterpriseToRevenue</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>totalRevenue</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>debtToEquity</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>revenuePerShare</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>grossProfits</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -2899,7 +2934,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Nicholas Simon Beal', 'age': 54, 'title': 'CEO, Chief Restructuring Officer, Company Secretary &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 428018, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mark  Hamer', 'title': 'Head of Financial Reporting', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Anil Kumar Reddy Yerrapareddy', 'title': 'Chief Executive Officer of African Mining Operations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Nicholas Simon Beal', 'age': 54, 'title': 'CEO, Chief Restructuring Officer, Company Secretary &amp; Executive Director', 'yearBorn': 1971, 'fiscalYear': 2025, 'totalPay': 427077, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mark  Hamer', 'title': 'Head of Financial Reporting', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Anil Kumar Reddy Yerrapareddy', 'title': 'Chief Executive Officer of African Mining Operations', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -2918,7 +2953,7 @@
         <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1767139200</v>
@@ -2938,31 +2973,31 @@
         <v>0.0255</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0225</v>
+        <v>0.024</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0215</v>
+        <v>0.024</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0225</v>
+        <v>0.0275</v>
       </c>
       <c r="AD2" t="n">
         <v>0.0255</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0225</v>
+        <v>0.024</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0215</v>
+        <v>0.024</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0225</v>
+        <v>0.0275</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.938</v>
+        <v>2.056</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -2985,16 +3020,16 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0215</v>
+        <v>0.0275</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="AR2" t="n">
-        <v>25586896</v>
+        <v>36569468</v>
       </c>
       <c r="AS2" t="n">
-        <v>34355240</v>
+        <v>40217951</v>
       </c>
       <c r="AT2" t="n">
         <v>0.0015</v>
@@ -3009,300 +3044,321 @@
         <v>0.0005</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02544</v>
+        <v>-60.949112</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0119075</v>
+        <v>0.02468</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.0133575</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8132941</v>
+      <c r="BD2" t="b">
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>24762116</v>
       </c>
       <c r="BF2" t="n">
-        <v>353715795</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1190088160</v>
+        <v>667788975</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.40589002</v>
+        <v>1329798836</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>0.36515</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1190088160</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>1329798836</v>
       </c>
       <c r="BL2" t="n">
+        <v>0.001153256</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>23.845528</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1759190400</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BO2" t="n">
         <v>1790726400</v>
       </c>
-      <c r="BN2" t="n">
-        <v>1743379200</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>47200024</v>
-      </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1774915200</v>
       </c>
       <c r="BQ2" t="n">
+        <v>45100024</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-41.27</v>
+      </c>
+      <c r="BT2" t="n">
         <v>16</v>
       </c>
-      <c r="BR2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BU2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BV2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BT2" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BW2" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="BX2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BV2" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
       <c r="BY2" t="n">
-        <v>0.875</v>
+        <v>1100000</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.875</v>
+        <v>0.001</v>
       </c>
       <c r="CA2" t="n">
-        <v>-133333</v>
+        <v>600000</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.44444</v>
-      </c>
-      <c r="CE2" t="inlineStr">
+        <v>-600000</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>4666667</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>4.05556</v>
+      </c>
+      <c r="CL2" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>0VG.F</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CS2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CU2" t="n">
+        <v>1782154434</v>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>finmb_404506816</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>7.843139</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1596434400000</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.0020000003</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.024 - 0.0275</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Amigo Resources PLC           R</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Amigo Resources PLC</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>Amigo Resources PLC           R</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CP2" t="n">
-        <v>1780429314</v>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>finmb_404506816</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="CU2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="CW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>-0.0039399993</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>-0.15487419</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.0095925005</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0.8055847</v>
-      </c>
-      <c r="DB2" t="n">
+      <c r="DL2" t="n">
+        <v>0.00282</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.114262566</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.0141425</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1.0587685</v>
+      </c>
+      <c r="DP2" t="n">
         <v>15</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DQ2" t="n">
         <v>15</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>Amigo Holdings PLC</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Amigo Resources PLC</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1596434400000</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.003999999</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>0.0215 - 0.0225</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.020000001</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>13.333334</v>
-      </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>17.333334</v>
+      </c>
+      <c r="DY2" t="inlineStr">
         <is>
           <t>0.0015 - 0.0305</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.29508194</v>
-      </c>
-      <c r="DS2" t="n">
+      <c r="DZ2" t="n">
+        <v>-0.0030000005</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.09836067</v>
+      </c>
+      <c r="EB2" t="n">
         <v>1600</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EC2" t="n">
         <v>1746165603</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="ED2" t="n">
         <v>1746165603</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EE2" t="n">
         <v>1721908800</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EF2" t="n">
         <v>1721908800</v>
       </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-15.686271</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="EB2" t="inlineStr"/>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
